--- a/public/exports-from-60-with-coowners/29189773.xlsx
+++ b/public/exports-from-60-with-coowners/29189773.xlsx
@@ -11089,12 +11089,12 @@
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t xml:space="preserve">311086998</t>
+          <t xml:space="preserve">311086994</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t xml:space="preserve">factum2 Kolding</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M148" t="inlineStr">
@@ -11389,12 +11389,12 @@
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t xml:space="preserve">311087002</t>
+          <t xml:space="preserve">311086999</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t xml:space="preserve">factum2 Kolding</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M152" t="inlineStr">
@@ -11614,12 +11614,12 @@
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t xml:space="preserve">311087012</t>
+          <t xml:space="preserve">311087008</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">factum2 Kolding</t>
         </is>
       </c>
       <c r="M155" t="inlineStr">
@@ -11764,12 +11764,12 @@
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t xml:space="preserve">311087009</t>
+          <t xml:space="preserve">311086987</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">factum2 Kolding</t>
         </is>
       </c>
       <c r="M157" t="inlineStr">
@@ -25639,12 +25639,12 @@
       </c>
       <c r="K342" t="inlineStr">
         <is>
-          <t xml:space="preserve">311884431</t>
+          <t xml:space="preserve">311884429</t>
         </is>
       </c>
       <c r="L342" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M342" t="inlineStr">
@@ -25789,12 +25789,12 @@
       </c>
       <c r="K344" t="inlineStr">
         <is>
-          <t xml:space="preserve">311884430</t>
+          <t xml:space="preserve">311884429</t>
         </is>
       </c>
       <c r="L344" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M344" t="inlineStr">
@@ -26914,7 +26914,7 @@
       </c>
       <c r="K359" t="inlineStr">
         <is>
-          <t xml:space="preserve">311900367</t>
+          <t xml:space="preserve">311900366</t>
         </is>
       </c>
       <c r="L359" t="inlineStr">
